--- a/dados/dados_documentos.xlsx
+++ b/dados/dados_documentos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bruno.marra\Documents\Gerador_De_Documentos\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC495D7-44EE-4280-A105-2C61C4564289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56A53EA-FD44-48AC-A2DF-4101A89B83CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>CAMINHO</t>
   </si>
@@ -73,15 +73,9 @@
     <t>modelosPadrao\</t>
   </si>
   <si>
-    <t>ASSINATURA DO CONTRATO</t>
-  </si>
-  <si>
     <t>.docx</t>
   </si>
   <si>
-    <t>modelosPadrao\ASSINATURA DO CONTRATO.docx</t>
-  </si>
-  <si>
     <t>pbh</t>
   </si>
   <si>
@@ -98,12 +92,6 @@
   </si>
   <si>
     <t>modelosPadrao\CARTA PROPOSTA.docx</t>
-  </si>
-  <si>
-    <t>DECLARACAO CONJUNTA</t>
-  </si>
-  <si>
-    <t>modelosPadrao\DECLARACAO CONJUNTA.docx</t>
   </si>
 </sst>
 </file>
@@ -111,7 +99,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -167,7 +155,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -531,16 +519,16 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
       <c r="F2">
         <v>31</v>
@@ -549,131 +537,31 @@
         <v>45967</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2">
-        <v>45967</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>31</v>
-      </c>
-      <c r="G4" s="2">
-        <v>45967</v>
-      </c>
-      <c r="H4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" t="s">
-        <v>23</v>
-      </c>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
